--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-ti-flow-capability-statement.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-ti-flow-capability-statement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5584" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5573" uniqueCount="641">
   <si>
     <t>Property</t>
   </si>
@@ -271,8 +271,8 @@
     <t>Applications may implement multiple versions (see [Managing Multiple Versions](http://hl7.org/fhir/R4/versioning.html), and the [$versions](http://hl7.org/fhir/R4/capabilitystatement-operation-versions.html) operation). If they do, then a CapabilityStatement describes the system's support for a particular version of FHIR, and the server will have multiple statements, one for each version.</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}cpb-7:The set of documents must be unique by the combination of profile and mode. {document.select(profile&amp;mode).isDistinct()}cpb-16:If kind = requirements, implementation and software must be absent {(kind!='requirements') or (implementation.exists().not() and software.exists().not())}cpb-15:If kind = capability, implementation must be absent, software must be present {(kind != 'capability') or (implementation.exists().not() and software.exists())}cpb-3:Messaging end-point is required (and is only permitted) when a statement is for an implementation. {messaging.endpoint.empty() or kind = 'instance'}cpb-14:If kind = instance, implementation must be present and software may be present {(kind != 'instance') or implementation.exists()}cpb-2:A Capability Statement SHALL have at least one of description, software, or implementation element. {(description.count() + software.count() + implementation.count()) &gt; 0}cpb-1:A Capability Statement SHALL have at least one of REST, messaging or document element. {rest.exists() or messaging.exists() or document.exists()}cpb-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}</t>
+    <t>cpb-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}
+cpb-1:A Capability Statement SHALL have at least one of REST, messaging or document element. {rest.exists() or messaging.exists() or document.exists()}cpb-2:A Capability Statement SHALL have at least one of description, software, or implementation element. {(description.count() + software.count() + implementation.count()) &gt; 0}cpb-3:Messaging end-point is required (and is only permitted) when a statement is for an implementation. {messaging.endpoint.empty() or kind = 'instance'}cpb-7:The set of documents must be unique by the combination of profile and mode. {document.select(profile&amp;mode).isDistinct()}cpb-14:If kind = instance, implementation must be present and software may be present {(kind != 'instance') or implementation.exists()}cpb-15:If kind = capability, implementation must be absent, software must be present {(kind != 'capability') or (implementation.exists().not() and software.exists())}cpb-16:If kind = requirements, implementation and software must be absent {(kind!='requirements') or (implementation.exists().not() and software.exists().not())}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>n/a</t>
@@ -364,7 +364,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -446,9 +446,6 @@
 </t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>open</t>
   </si>
   <si>
@@ -473,6 +470,10 @@
   </si>
   <si>
     <t>Gibt die Basis-URL des FHIR-Servers als Zeichenkette an. Beispiel: http://epa4all/epa/medication/api/v1/fhir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>CapabilityStatement.extension:header</t>
@@ -774,10 +775,6 @@
     <t>May be a web site, an email address, a telephone number, etc.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Definition.contact</t>
   </si>
   <si>
@@ -848,10 +845,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -891,9 +885,6 @@
     <t>A copyright statement relating to the capability statement and/or its contents. Copyright statements are generally legal restrictions on the use and publishing of the capability statement.</t>
   </si>
   <si>
-    <t>Systems are not required to have markdown support, so the text should be readable without markdown processing. The markdown syntax is GFM - see https://github.github.com/gfm/</t>
-  </si>
-  <si>
     <t>Consumers must be able to determine any legal restrictions on the use of the capability statement and/or its content.</t>
   </si>
   <si>
@@ -925,7 +916,7 @@
     <t>CapabilityStatement.instantiates</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(CapabilityStatement|4.0.1)
+    <t xml:space="preserve">canonical(CapabilityStatement)
 </t>
   </si>
   <si>
@@ -965,10 +956,6 @@
     <t>Software that is covered by this capability statement.  It is used when the capability statement describes the capabilities of a particular software version, independent of an installation.</t>
   </si>
   <si>
-    <t>ele-1
-cpb-2</t>
-  </si>
-  <si>
     <t>CapabilityStatement.software.id</t>
   </si>
   <si>
@@ -1016,9 +1003,6 @@
     <t>Name the software is known by.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>CapabilityStatement.software.version</t>
   </si>
   <si>
@@ -1049,8 +1033,8 @@
     <t>Identifies a specific implementation instance that is described by the capability statement - i.e. a particular installation, rather than the capabilities of a software program.</t>
   </si>
   <si>
-    <t>ele-1
-cpb-2cpb-15</t>
+    <t>cpb-2
+cpb-15</t>
   </si>
   <si>
     <t>CapabilityStatement.implementation.id</t>
@@ -1087,7 +1071,7 @@
     <t>CapabilityStatement.implementation.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1097,16 +1081,6 @@
     <t>The organization responsible for the management of the instance and oversight of the data on the server at the specified URL.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
     <t>CapabilityStatement.fhirVersion</t>
   </si>
   <si>
@@ -1158,7 +1132,7 @@
     <t>CapabilityStatement.implementationGuide</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ImplementationGuide|4.0.1)
+    <t xml:space="preserve">canonical(ImplementationGuide)
 </t>
   </si>
   <si>
@@ -1168,9 +1142,6 @@
     <t>A list of implementation guides that the server does (or should) support in their entirety.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>CapabilityStatement.rest</t>
   </si>
   <si>
@@ -1183,12 +1154,12 @@
     <t>Multiple repetitions allow definition of both client and/or server behaviors or possibly behaviors under different configuration settings (for software or requirements statements).</t>
   </si>
   <si>
-    <t>ele-1
-cpb-1</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cpb-9:A given resource can only be described once per RESTful mode. {resource.select(type).isDistinct()}</t>
+    <t xml:space="preserve">cpb-1
+</t>
+  </si>
+  <si>
+    <t>cpb-9:A given resource can only be described once per RESTful mode. {resource.select(type).isDistinct()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>CapabilityStatement.rest.id</t>
@@ -1263,13 +1234,10 @@
     <t>Types of security services that are supported/required by the system.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>Types of security services used with FHIR.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/restful-security-service|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/restful-security-service</t>
   </si>
   <si>
     <t>CapabilityStatement.rest.security.description</t>
@@ -1293,8 +1261,8 @@
     <t>Max of one repetition per resource type.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cpb-12:Search parameter names must be unique in the context of a resource. {searchParam.select(name).isDistinct()}</t>
+    <t>cpb-12:Search parameter names must be unique in the context of a resource. {searchParam.select(name).isDistinct()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>CapabilityStatement.rest.resource.id</t>
@@ -1324,7 +1292,7 @@
     <t>CapabilityStatement.rest.resource.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -1599,7 +1567,7 @@
     <t>CapabilityStatement.rest.resource.searchParam.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(SearchParameter|4.0.1)
+    <t xml:space="preserve">canonical(SearchParameter)
 </t>
   </si>
   <si>
@@ -1704,7 +1672,7 @@
     <t>CapabilityStatement.rest.resource.operation.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(OperationDefinition|4.0.1)
+    <t xml:space="preserve">canonical(OperationDefinition)
 </t>
   </si>
   <si>
@@ -1819,7 +1787,7 @@
     <t>CapabilityStatement.rest.compartment</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(CompartmentDefinition|4.0.1)
+    <t xml:space="preserve">canonical(CompartmentDefinition)
 </t>
   </si>
   <si>
@@ -1888,16 +1856,10 @@
     <t>A list of the messaging transport protocol(s) identifiers, supported by this endpoint.</t>
   </si>
   <si>
-    <t>Codes may be defined very casually in enumerations or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.</t>
-  </si>
-  <si>
     <t>The protocol used for message transport.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/message-transport|4.0.1</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>http://hl7.org/fhir/ValueSet/message-transport</t>
   </si>
   <si>
     <t>CapabilityStatement.messaging.endpoint.address</t>
@@ -1973,7 +1935,7 @@
     <t>CapabilityStatement.messaging.supportedMessage.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(MessageDefinition|4.0.1)
+    <t xml:space="preserve">canonical(MessageDefinition)
 </t>
   </si>
   <si>
@@ -2371,14 +2333,14 @@
     <col min="26" max="26" width="47.3671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="51.16796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="60.26953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
@@ -3379,17 +3341,15 @@
       <c r="AB9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AC9" t="s" s="2">
+      <c r="AC9" s="2"/>
+      <c r="AD9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE9" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AD9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE9" t="s" s="2">
+      <c r="AF9" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3401,7 +3361,7 @@
         <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>131</v>
@@ -3418,16 +3378,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3446,15 +3406,17 @@
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
@@ -3503,7 +3465,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3512,13 +3474,13 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>78</v>
@@ -3541,7 +3503,7 @@
         <v>149</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3568,7 +3530,9 @@
       <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>78</v>
@@ -3617,7 +3581,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3626,13 +3590,13 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>78</v>
@@ -3655,7 +3619,7 @@
         <v>154</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3682,7 +3646,9 @@
       <c r="M12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N12" s="2"/>
+      <c r="N12" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>78</v>
@@ -3731,7 +3697,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3740,13 +3706,13 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>78</v>
@@ -3847,7 +3813,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3859,7 +3825,7 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
@@ -3963,7 +3929,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3975,7 +3941,7 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -4079,7 +4045,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4091,7 +4057,7 @@
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -4183,16 +4149,16 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>180</v>
@@ -4207,7 +4173,7 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>131</v>
@@ -5238,16 +5204,16 @@
         <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -5258,10 +5224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5284,16 +5250,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5343,7 +5309,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5352,7 +5318,7 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>100</v>
@@ -5361,7 +5327,7 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -5372,10 +5338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5398,19 +5364,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5459,7 +5425,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5468,16 +5434,16 @@
         <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5488,10 +5454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5514,16 +5480,16 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5549,14 +5515,14 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Y28" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5573,7 +5539,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5582,16 +5548,16 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5602,10 +5568,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5628,16 +5594,16 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5687,7 +5653,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5705,25 +5671,25 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>275</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5742,19 +5708,17 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5803,7 +5767,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5821,21 +5785,21 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5861,14 +5825,14 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5896,10 +5860,10 @@
         <v>210</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5917,7 +5881,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>88</v>
@@ -5926,7 +5890,7 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
@@ -5946,10 +5910,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5972,16 +5936,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6031,7 +5995,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6060,10 +6024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6086,16 +6050,16 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6145,7 +6109,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6174,10 +6138,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6200,13 +6164,13 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6257,7 +6221,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6266,13 +6230,13 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>303</v>
+        <v>249</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
@@ -6286,10 +6250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6315,10 +6279,10 @@
         <v>189</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6369,7 +6333,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6398,10 +6362,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6430,7 +6394,7 @@
         <v>135</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>137</v>
@@ -6471,19 +6435,19 @@
         <v>78</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6495,7 +6459,7 @@
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>86</v>
@@ -6512,14 +6476,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6541,10 +6505,10 @@
         <v>134</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>137</v>
@@ -6599,7 +6563,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6611,7 +6575,7 @@
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>131</v>
@@ -6628,10 +6592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6657,14 +6621,12 @@
         <v>189</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6713,7 +6675,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>88</v>
@@ -6742,10 +6704,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6771,13 +6733,13 @@
         <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6827,7 +6789,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6856,10 +6818,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6885,10 +6847,10 @@
         <v>225</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6939,7 +6901,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6968,10 +6930,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6994,13 +6956,13 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7051,7 +7013,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7060,13 +7022,13 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>78</v>
@@ -7080,10 +7042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7109,10 +7071,10 @@
         <v>189</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7163,7 +7125,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7192,10 +7154,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7224,7 +7186,7 @@
         <v>135</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>137</v>
@@ -7265,19 +7227,19 @@
         <v>78</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7289,7 +7251,7 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>86</v>
@@ -7306,14 +7268,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7335,10 +7297,10 @@
         <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>137</v>
@@ -7393,7 +7355,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7405,7 +7367,7 @@
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>131</v>
@@ -7422,10 +7384,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7451,14 +7413,12 @@
         <v>189</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7507,7 +7467,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>88</v>
@@ -7536,10 +7496,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7562,13 +7522,13 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7619,7 +7579,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7648,10 +7608,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7674,17 +7634,15 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7733,7 +7691,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7742,13 +7700,13 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>346</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7762,10 +7720,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7791,13 +7749,13 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7826,10 +7784,10 @@
         <v>210</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7847,7 +7805,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>88</v>
@@ -7876,10 +7834,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7905,13 +7863,13 @@
         <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7940,10 +7898,10 @@
         <v>210</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7961,7 +7919,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>88</v>
@@ -7990,10 +7948,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8019,13 +7977,13 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8054,10 +8012,10 @@
         <v>210</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8075,7 +8033,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8104,10 +8062,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8130,17 +8088,15 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8189,7 +8145,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8218,10 +8174,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8244,16 +8200,16 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8303,7 +8259,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8312,13 +8268,13 @@
         <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>78</v>
@@ -8332,10 +8288,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8361,10 +8317,10 @@
         <v>189</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8415,7 +8371,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8444,10 +8400,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8476,7 +8432,7 @@
         <v>135</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>137</v>
@@ -8517,19 +8473,19 @@
         <v>78</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8541,7 +8497,7 @@
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>86</v>
@@ -8558,14 +8514,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8587,10 +8543,10 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>137</v>
@@ -8645,7 +8601,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8657,7 +8613,7 @@
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>131</v>
@@ -8674,10 +8630,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8703,10 +8659,10 @@
         <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8736,10 +8692,10 @@
         <v>210</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8757,7 +8713,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>88</v>
@@ -8786,10 +8742,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8812,17 +8768,15 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8871,7 +8825,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8900,10 +8854,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8926,13 +8880,13 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8983,7 +8937,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8992,13 +8946,13 @@
         <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>78</v>
@@ -9012,10 +8966,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9041,10 +8995,10 @@
         <v>189</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9095,7 +9049,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9124,10 +9078,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9156,7 +9110,7 @@
         <v>135</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>137</v>
@@ -9197,19 +9151,19 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9221,7 +9175,7 @@
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>86</v>
@@ -9238,14 +9192,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9267,10 +9221,10 @@
         <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>137</v>
@@ -9325,7 +9279,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9337,7 +9291,7 @@
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>131</v>
@@ -9354,10 +9308,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9383,13 +9337,13 @@
         <v>216</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9439,7 +9393,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9468,10 +9422,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9494,17 +9448,15 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9529,13 +9481,13 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9553,7 +9505,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9562,13 +9514,13 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>78</v>
@@ -9582,10 +9534,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9608,17 +9560,15 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9667,7 +9617,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9696,10 +9646,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9722,16 +9672,16 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9781,7 +9731,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9790,13 +9740,13 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>78</v>
@@ -9810,10 +9760,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9839,10 +9789,10 @@
         <v>189</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9893,7 +9843,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9922,10 +9872,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9954,7 +9904,7 @@
         <v>135</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>137</v>
@@ -9995,19 +9945,19 @@
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10019,7 +9969,7 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>86</v>
@@ -10036,14 +9986,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10065,10 +10015,10 @@
         <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>137</v>
@@ -10123,7 +10073,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10135,7 +10085,7 @@
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>131</v>
@@ -10152,10 +10102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10181,10 +10131,10 @@
         <v>108</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10214,10 +10164,10 @@
         <v>210</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -10235,7 +10185,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>88</v>
@@ -10264,10 +10214,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10290,16 +10240,16 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10349,7 +10299,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10378,10 +10328,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10404,16 +10354,16 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10463,7 +10413,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10492,10 +10442,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10518,17 +10468,15 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10577,7 +10525,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10606,10 +10554,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10632,16 +10580,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10691,7 +10639,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10700,13 +10648,13 @@
         <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>78</v>
@@ -10720,10 +10668,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10749,10 +10697,10 @@
         <v>189</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10803,7 +10751,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10832,10 +10780,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10864,7 +10812,7 @@
         <v>135</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>137</v>
@@ -10907,17 +10855,15 @@
       <c r="AB75" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AC75" t="s" s="2">
+      <c r="AC75" s="2"/>
+      <c r="AD75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE75" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AD75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>140</v>
-      </c>
       <c r="AF75" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10929,7 +10875,7 @@
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>86</v>
@@ -10946,16 +10892,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>149</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10982,7 +10928,9 @@
       <c r="M76" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N76" s="2"/>
+      <c r="N76" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11031,7 +10979,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11040,13 +10988,13 @@
         <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>78</v>
@@ -11060,16 +11008,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>154</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11096,7 +11044,9 @@
       <c r="M77" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N77" s="2"/>
+      <c r="N77" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11145,7 +11095,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11154,13 +11104,13 @@
         <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>78</v>
@@ -11174,16 +11124,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11202,16 +11152,16 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11261,7 +11211,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11270,10 +11220,10 @@
         <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>131</v>
@@ -11290,14 +11240,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11319,10 +11269,10 @@
         <v>134</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>137</v>
@@ -11377,7 +11327,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11389,7 +11339,7 @@
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>131</v>
@@ -11406,10 +11356,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11435,10 +11385,10 @@
         <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11468,10 +11418,10 @@
         <v>210</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11489,7 +11439,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>88</v>
@@ -11518,10 +11468,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11544,19 +11494,17 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -11605,7 +11553,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11634,10 +11582,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11663,13 +11611,13 @@
         <v>108</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11698,10 +11646,10 @@
         <v>210</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11719,7 +11667,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11748,10 +11696,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11777,13 +11725,13 @@
         <v>216</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11833,7 +11781,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11862,10 +11810,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11891,13 +11839,13 @@
         <v>216</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11947,7 +11895,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11976,10 +11924,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12005,13 +11953,13 @@
         <v>216</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12061,7 +12009,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12090,10 +12038,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12119,13 +12067,13 @@
         <v>108</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12154,10 +12102,10 @@
         <v>210</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -12175,7 +12123,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12204,10 +12152,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12233,13 +12181,13 @@
         <v>216</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12289,7 +12237,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12318,10 +12266,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12347,13 +12295,13 @@
         <v>108</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12382,10 +12330,10 @@
         <v>210</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -12403,7 +12351,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12432,10 +12380,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12461,10 +12409,10 @@
         <v>108</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12494,10 +12442,10 @@
         <v>210</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
@@ -12515,7 +12463,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12544,10 +12492,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12573,13 +12521,13 @@
         <v>189</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12629,7 +12577,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12658,10 +12606,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12687,13 +12635,13 @@
         <v>189</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12743,7 +12691,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12772,10 +12720,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12798,16 +12746,16 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12857,7 +12805,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12866,13 +12814,13 @@
         <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>78</v>
@@ -12886,10 +12834,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12915,10 +12863,10 @@
         <v>189</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12969,7 +12917,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12998,10 +12946,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13030,7 +12978,7 @@
         <v>135</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>137</v>
@@ -13071,19 +13019,19 @@
         <v>78</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13095,7 +13043,7 @@
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>86</v>
@@ -13112,14 +13060,14 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13141,10 +13089,10 @@
         <v>134</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>137</v>
@@ -13199,7 +13147,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13211,7 +13159,7 @@
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>131</v>
@@ -13228,10 +13176,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13257,13 +13205,13 @@
         <v>189</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13313,7 +13261,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>88</v>
@@ -13342,10 +13290,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13368,16 +13316,16 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13427,7 +13375,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13456,10 +13404,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13485,13 +13433,13 @@
         <v>108</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13520,10 +13468,10 @@
         <v>210</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13541,7 +13489,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>88</v>
@@ -13570,10 +13518,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13596,17 +13544,15 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13655,7 +13601,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13684,10 +13630,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13710,16 +13656,16 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13769,7 +13715,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13778,13 +13724,13 @@
         <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>78</v>
@@ -13798,10 +13744,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13827,10 +13773,10 @@
         <v>189</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13881,7 +13827,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13910,10 +13856,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13942,7 +13888,7 @@
         <v>135</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>137</v>
@@ -13985,17 +13931,15 @@
       <c r="AB102" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AC102" t="s" s="2">
+      <c r="AC102" s="2"/>
+      <c r="AD102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE102" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AD102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>140</v>
-      </c>
       <c r="AF102" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14007,7 +13951,7 @@
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>86</v>
@@ -14024,16 +13968,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>149</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14060,7 +14004,9 @@
       <c r="M103" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N103" s="2"/>
+      <c r="N103" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14109,7 +14055,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14118,13 +14064,13 @@
         <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>78</v>
@@ -14138,16 +14084,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>154</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14174,7 +14120,9 @@
       <c r="M104" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N104" s="2"/>
+      <c r="N104" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14223,7 +14171,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14232,13 +14180,13 @@
         <v>80</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>78</v>
@@ -14252,23 +14200,23 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>78</v>
@@ -14280,15 +14228,17 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14337,7 +14287,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14346,13 +14296,13 @@
         <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>78</v>
@@ -14366,16 +14316,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14394,16 +14344,16 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14453,7 +14403,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14462,10 +14412,10 @@
         <v>80</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>131</v>
@@ -14482,14 +14432,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -14511,10 +14461,10 @@
         <v>134</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>137</v>
@@ -14569,7 +14519,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14581,7 +14531,7 @@
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>131</v>
@@ -14598,10 +14548,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14627,13 +14577,13 @@
         <v>189</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14683,7 +14633,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>88</v>
@@ -14712,10 +14662,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14738,16 +14688,16 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14797,7 +14747,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>88</v>
@@ -14826,10 +14776,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14852,17 +14802,15 @@
         <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -14911,7 +14859,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14940,10 +14888,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14966,13 +14914,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15023,7 +14971,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15032,13 +14980,13 @@
         <v>80</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>78</v>
@@ -15052,10 +15000,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15081,10 +15029,10 @@
         <v>189</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15135,7 +15083,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15164,10 +15112,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15196,7 +15144,7 @@
         <v>135</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>137</v>
@@ -15237,19 +15185,19 @@
         <v>78</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15261,7 +15209,7 @@
         <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>86</v>
@@ -15278,14 +15226,14 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15307,10 +15255,10 @@
         <v>134</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>137</v>
@@ -15365,7 +15313,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15377,7 +15325,7 @@
         <v>78</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>131</v>
@@ -15394,10 +15342,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15423,10 +15371,10 @@
         <v>108</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15456,10 +15404,10 @@
         <v>210</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>78</v>
@@ -15477,7 +15425,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>88</v>
@@ -15506,10 +15454,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15532,17 +15480,15 @@
         <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -15591,7 +15537,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15620,10 +15566,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15649,13 +15595,13 @@
         <v>81</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15705,7 +15651,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15717,7 +15663,7 @@
         <v>78</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>78</v>
@@ -15734,10 +15680,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15760,16 +15706,16 @@
         <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15819,7 +15765,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -15831,7 +15777,7 @@
         <v>78</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>78</v>
@@ -15848,10 +15794,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15877,10 +15823,10 @@
         <v>189</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15931,7 +15877,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15960,10 +15906,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15992,7 +15938,7 @@
         <v>135</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>137</v>
@@ -16035,17 +15981,15 @@
       <c r="AB120" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AC120" t="s" s="2">
+      <c r="AC120" s="2"/>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AD120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>140</v>
-      </c>
       <c r="AF120" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16057,7 +16001,7 @@
         <v>78</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>86</v>
@@ -16074,16 +16018,16 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>149</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -16110,7 +16054,9 @@
       <c r="M121" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N121" s="2"/>
+      <c r="N121" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>78</v>
@@ -16159,7 +16105,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16168,13 +16114,13 @@
         <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>78</v>
@@ -16188,16 +16134,16 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>154</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16224,7 +16170,9 @@
       <c r="M122" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N122" s="2"/>
+      <c r="N122" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16273,7 +16221,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16282,13 +16230,13 @@
         <v>80</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>78</v>
@@ -16302,23 +16250,23 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>78</v>
@@ -16330,15 +16278,17 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16387,7 +16337,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16396,13 +16346,13 @@
         <v>80</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>78</v>
@@ -16416,16 +16366,16 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -16444,16 +16394,16 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -16503,7 +16453,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16512,10 +16462,10 @@
         <v>80</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>131</v>
@@ -16532,14 +16482,14 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -16561,10 +16511,10 @@
         <v>134</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>137</v>
@@ -16619,7 +16569,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16631,7 +16581,7 @@
         <v>78</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>131</v>
@@ -16648,10 +16598,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16677,13 +16627,13 @@
         <v>189</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -16733,7 +16683,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>88</v>
@@ -16762,10 +16712,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16788,16 +16738,16 @@
         <v>89</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16847,7 +16797,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>88</v>
@@ -16876,10 +16826,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16902,17 +16852,15 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -16961,7 +16909,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16990,10 +16938,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17016,16 +16964,16 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17075,7 +17023,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17104,10 +17052,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17130,16 +17078,16 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17189,7 +17137,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17198,13 +17146,13 @@
         <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>78</v>
@@ -17218,10 +17166,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17247,10 +17195,10 @@
         <v>189</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17301,7 +17249,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17330,10 +17278,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17362,7 +17310,7 @@
         <v>135</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>137</v>
@@ -17403,19 +17351,19 @@
         <v>78</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17427,7 +17375,7 @@
         <v>78</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>86</v>
@@ -17444,14 +17392,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -17473,10 +17421,10 @@
         <v>134</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>137</v>
@@ -17531,7 +17479,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17543,7 +17491,7 @@
         <v>78</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>131</v>
@@ -17560,14 +17508,14 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -17586,13 +17534,13 @@
         <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -17643,7 +17591,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17652,13 +17600,13 @@
         <v>80</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>78</v>
@@ -17672,10 +17620,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17701,10 +17649,10 @@
         <v>189</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17755,7 +17703,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17784,10 +17732,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17816,7 +17764,7 @@
         <v>135</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>137</v>
@@ -17857,19 +17805,19 @@
         <v>78</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -17881,7 +17829,7 @@
         <v>78</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>86</v>
@@ -17898,14 +17846,14 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -17927,10 +17875,10 @@
         <v>134</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>137</v>
@@ -17985,7 +17933,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17997,7 +17945,7 @@
         <v>78</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>131</v>
@@ -18014,10 +17962,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18040,17 +17988,15 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>604</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>78</v>
@@ -18075,13 +18021,13 @@
         <v>78</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>78</v>
@@ -18099,7 +18045,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>88</v>
@@ -18108,13 +18054,13 @@
         <v>88</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>607</v>
+        <v>78</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>78</v>
@@ -18128,10 +18074,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18154,13 +18100,13 @@
         <v>78</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18211,7 +18157,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>88</v>
@@ -18240,10 +18186,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18266,16 +18212,16 @@
         <v>78</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -18325,7 +18271,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18354,10 +18300,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18380,17 +18326,15 @@
         <v>78</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18439,7 +18383,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18468,10 +18412,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18494,16 +18438,16 @@
         <v>89</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18553,7 +18497,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18562,13 +18506,13 @@
         <v>80</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>78</v>
@@ -18582,10 +18526,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18611,10 +18555,10 @@
         <v>189</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18665,7 +18609,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18694,10 +18638,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18726,7 +18670,7 @@
         <v>135</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>137</v>
@@ -18767,19 +18711,19 @@
         <v>78</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -18791,7 +18735,7 @@
         <v>78</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>86</v>
@@ -18808,14 +18752,14 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -18837,10 +18781,10 @@
         <v>134</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N145" t="s" s="2">
         <v>137</v>
@@ -18895,7 +18839,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -18907,7 +18851,7 @@
         <v>78</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>131</v>
@@ -18924,10 +18868,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18953,10 +18897,10 @@
         <v>108</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -18986,10 +18930,10 @@
         <v>210</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>78</v>
@@ -19007,7 +18951,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>88</v>
@@ -19036,10 +18980,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19062,17 +19006,15 @@
         <v>89</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -19121,7 +19063,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>88</v>
@@ -19150,10 +19092,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19176,13 +19118,13 @@
         <v>89</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -19233,7 +19175,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19242,13 +19184,13 @@
         <v>80</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>78</v>
@@ -19262,10 +19204,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19291,10 +19233,10 @@
         <v>189</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -19345,7 +19287,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19374,10 +19316,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19406,7 +19348,7 @@
         <v>135</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>137</v>
@@ -19447,19 +19389,19 @@
         <v>78</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -19471,7 +19413,7 @@
         <v>78</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>86</v>
@@ -19488,14 +19430,14 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -19517,10 +19459,10 @@
         <v>134</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N151" t="s" s="2">
         <v>137</v>
@@ -19575,7 +19517,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -19587,7 +19529,7 @@
         <v>78</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>131</v>
@@ -19604,10 +19546,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19633,10 +19575,10 @@
         <v>108</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -19666,10 +19608,10 @@
         <v>210</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>78</v>
@@ -19687,7 +19629,7 @@
         <v>78</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>88</v>
@@ -19716,10 +19658,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19742,17 +19684,15 @@
         <v>78</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -19801,7 +19741,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -19830,10 +19770,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19856,16 +19796,16 @@
         <v>89</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -19915,7 +19855,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>88</v>
